--- a/Sistema-RRHH-2026.xlsx
+++ b/Sistema-RRHH-2026.xlsx
@@ -2,22 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6372EE84-58DF-4DAD-9021-36C423B27DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6372EE84-58DF-4DAD-9021-36C423B27DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B640BEA8-2C56-4921-BC89-663354CDCF27}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="24" windowWidth="11760" windowHeight="12240" xr2:uid="{A5EDE06E-7574-4FAF-8151-D165ADA9B625}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11760" windowHeight="12240" firstSheet="3" activeTab="3" xr2:uid="{A5EDE06E-7574-4FAF-8151-D165ADA9B625}"/>
   </bookViews>
   <sheets>
     <sheet name="Filtros Avanzado " sheetId="1" r:id="rId1"/>
     <sheet name="Dashboard RRHH_x0009_" sheetId="2" r:id="rId2"/>
+    <sheet name="Filtros Avanzado 2 " sheetId="3" r:id="rId3"/>
+    <sheet name="Dashboard Ventas" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filtros Avanzado '!$A$7:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Filtros Avanzado 2 '!$A$4:$H$20</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="2">'Filtros Avanzado 2 '!$A$17:$B$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>Sistema-RRHH-2026</t>
   </si>
@@ -186,15 +190,114 @@
   <si>
     <t>Informatico</t>
   </si>
+  <si>
+    <t>Base de Datos de Ventas 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendedor </t>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Producto</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Santo Domingo</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>La vega</t>
+  </si>
+  <si>
+    <t>Bonao</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Escritorio</t>
+  </si>
+  <si>
+    <t>Silla</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Impresora</t>
+  </si>
+  <si>
+    <t>Tecnologia</t>
+  </si>
+  <si>
+    <t>Muebles</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Total Ventas</t>
+  </si>
+  <si>
+    <t>Promedio Venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venta Mayor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venta Menor </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="173" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,8 +344,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -264,6 +382,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -324,6 +448,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -333,9 +460,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1667,6 +1825,1258 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Ventas Totales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Por Vendedor </a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total Ventas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$A$19:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Ana</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Luis</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pedro</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Filtros Avanzado 2 '!$B$19:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>102000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>47400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9AEA-4569-B099-728B39776121}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1771445088"/>
+        <c:axId val="1771445568"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1771445088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1771445568"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1771445568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1771445088"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Valor Promedio Por Venta</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$C$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Promedio Venta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$A$19:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Ana</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Luis</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pedro</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Filtros Avanzado 2 '!$C$19:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>25500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A071-4A78-A328-ADE46C588CBB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1771446048"/>
+        <c:axId val="1771443168"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1771446048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1771443168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1771443168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1771446048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Mayor Venta Registrada</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$D$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Venta Mayor </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B458-49DC-98DC-765DD561590A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B458-49DC-98DC-765DD561590A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-B458-49DC-98DC-765DD561590A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$A$19:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Ana</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Luis</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pedro</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Filtros Avanzado 2 '!$D$19:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-B458-49DC-98DC-765DD561590A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Menor Venta Registrada</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$E$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Venta Menor </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Filtros Avanzado 2 '!$A$19:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Ana</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Luis</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pedro</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Filtros Avanzado 2 '!$E$19:$E$21</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E183-4C91-ABBE-2478AD5EF70B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1771445088"/>
+        <c:axId val="1771448928"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1771445088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1771448928"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1771448928"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-[$$-2C0A]\ * #,##0_-;\-[$$-2C0A]\ * #,##0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1771445088"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1824,6 +3234,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -3350,6 +4920,2038 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3983,6 +7585,155 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1B0A26A-EDE7-6CAE-1071-1CF52A4E293F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>150080</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8176686-ACF1-0F4A-7B9E-1FF388F566FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>356815</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>89453</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2240067-275B-F9A7-6DB0-D62510A14E64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>7619</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2247DC5-AA84-4484-87DE-CB43F5ADED62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>406842</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>30479</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DBE0194-9EE5-B272-531C-CD90A07C7ECA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4300,6 +8051,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CBAC8F-666D-43FC-ABDC-D78EABB75DA5}">
+  <sheetPr codeName="Sheet1">
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4312,20 +8066,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -4722,13 +8476,13 @@
       <c r="E23" s="7"/>
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -4849,8 +8603,8 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:G22" xr:uid="{18CBAC8F-666D-43FC-ABDC-D78EABB75DA5}"/>
@@ -4865,10 +8619,519 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A23BEFD-8049-4E1E-AC37-51180C08910E}">
+  <sheetPr codeName="Sheet2">
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A9125B1-5D87-4456-B81E-A74E13A274E2}">
+  <sheetPr codeName="Sheet3" filterMode="1">
+    <tabColor theme="8"/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="24"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="26">
+        <v>101</v>
+      </c>
+      <c r="B5" s="21">
+        <v>46027</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="20">
+        <v>2</v>
+      </c>
+      <c r="H5" s="30">
+        <v>45000</v>
+      </c>
+      <c r="I5" s="24"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="26">
+        <v>102</v>
+      </c>
+      <c r="B6" s="21">
+        <v>46029</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="20">
+        <v>5</v>
+      </c>
+      <c r="H6" s="30">
+        <v>800</v>
+      </c>
+      <c r="I6" s="24"/>
+    </row>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26">
+        <v>103</v>
+      </c>
+      <c r="B7" s="21">
+        <v>46032</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="20">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20">
+        <v>1200</v>
+      </c>
+      <c r="I7" s="24"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="26">
+        <v>104</v>
+      </c>
+      <c r="B8" s="21">
+        <v>46034</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="20">
+        <v>3</v>
+      </c>
+      <c r="H8" s="30">
+        <v>3500</v>
+      </c>
+      <c r="I8" s="24"/>
+    </row>
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26">
+        <v>105</v>
+      </c>
+      <c r="B9" s="21">
+        <v>46037</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="20">
+        <v>2</v>
+      </c>
+      <c r="H9" s="20">
+        <v>9500</v>
+      </c>
+      <c r="I9" s="24"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>106</v>
+      </c>
+      <c r="B10" s="21">
+        <v>46040</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="20">
+        <v>1</v>
+      </c>
+      <c r="H10" s="30">
+        <v>45000</v>
+      </c>
+      <c r="I10" s="24"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="26">
+        <v>107</v>
+      </c>
+      <c r="B11" s="21">
+        <v>46042</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="20">
+        <v>2</v>
+      </c>
+      <c r="H11" s="30">
+        <v>8500</v>
+      </c>
+      <c r="I11" s="24"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="26">
+        <v>108</v>
+      </c>
+      <c r="B12" s="21">
+        <v>46044</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="20">
+        <v>4</v>
+      </c>
+      <c r="H12" s="30">
+        <v>3500</v>
+      </c>
+      <c r="I12" s="24"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="26">
+        <v>109</v>
+      </c>
+      <c r="B13" s="21">
+        <v>46047</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="20">
+        <v>2</v>
+      </c>
+      <c r="H13" s="30">
+        <v>1200</v>
+      </c>
+      <c r="I13" s="24"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="26">
+        <v>110</v>
+      </c>
+      <c r="B14" s="21">
+        <v>46050</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="20">
+        <v>1</v>
+      </c>
+      <c r="H14" s="30">
+        <v>45000</v>
+      </c>
+      <c r="I14" s="24"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="24"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="31">
+        <f>SUMIF($C$5:$C$14, A19, $H$5:$H$14)</f>
+        <v>102000</v>
+      </c>
+      <c r="C19" s="32">
+        <f>AVERAGEIF($C$5:$C$14, A19, $H$5:$H$14)</f>
+        <v>25500</v>
+      </c>
+      <c r="D19" s="32">
+        <f>_xlfn.MAXIFS($H$5:$H$14,$C$5:$C$14,A19)</f>
+        <v>45000</v>
+      </c>
+      <c r="E19" s="32">
+        <f>_xlfn.MINIFS($H$5:$H$14,$C$5:$C$14,A19)</f>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="31">
+        <f t="shared" ref="B20:B21" si="0">SUMIF($C$5:$C$14, A20, $H$5:$H$14)</f>
+        <v>13800</v>
+      </c>
+      <c r="C20" s="32">
+        <f t="shared" ref="C20:C21" si="1">AVERAGEIF($C$5:$C$14, A20, $H$5:$H$14)</f>
+        <v>4600</v>
+      </c>
+      <c r="D20" s="32">
+        <f t="shared" ref="D20:D21" si="2">_xlfn.MAXIFS($H$5:$H$14,$C$5:$C$14,A20)</f>
+        <v>9500</v>
+      </c>
+      <c r="E20" s="32">
+        <f t="shared" ref="E20:E21" si="3">_xlfn.MINIFS($H$5:$H$14,$C$5:$C$14,A20)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="31">
+        <f>SUMIF($C$5:$C$14, A21, $H$5:$H$14)</f>
+        <v>47400</v>
+      </c>
+      <c r="C21" s="32">
+        <f t="shared" si="1"/>
+        <v>15800</v>
+      </c>
+      <c r="D21" s="32">
+        <f t="shared" si="2"/>
+        <v>45000</v>
+      </c>
+      <c r="E21" s="32">
+        <f>_xlfn.MINIFS(H5:H14,C5:C14,A21)</f>
+        <v>1200</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H20" xr:uid="{8A9125B1-5D87-4456-B81E-A74E13A274E2}">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="Ciudad"/>
+        <filter val="Santiago"/>
+        <dateGroupItem year="2026" month="1" day="5" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="1" day="7" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="1" day="12" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="1" day="18" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="1" day="20" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="1" day="22" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="1" day="25" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="1" day="28" dateTimeGrouping="day"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19CEAD5E-4320-448A-AAB1-D3B6A013135D}">
+  <sheetPr codeName="Sheet4">
+    <tabColor theme="8" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>